--- a/data/trans_dic/P15E_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P15E_R-Edad-trans_dic.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población mayor de 65 años que ha sufrido alguna caída que precise atención sanitaria en el último año</t>
+          <t>Población mayor de 65 años que ha sufrido alguna caída que precise atención sanitaria en el último año (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -539,7 +539,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>16-24</t>
+          <t>65-74</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>58,46%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,95%</t>
         </is>
       </c>
     </row>
@@ -572,24 +572,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>35,31; 79,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>52,62; 77,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>52,09; 74,11</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>75 o más</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,42%</t>
         </is>
       </c>
     </row>
@@ -622,24 +622,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>50,77; 81,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>66,17; 83,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>64,78; 80,4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>69,92%</t>
         </is>
       </c>
     </row>
@@ -672,288 +672,33 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>50,07; 77,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>64,85; 78,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>63,4; 75,62</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>45-54</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>55-64</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>65-74</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>58,46%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>66,41%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>63,95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n"/>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>35,76; 80,32</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>53,39; 77,73</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>52,91; 73,44</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>75 o más</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>68,66%</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>75,29%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>73,42%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>51,7; 82,37</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>66,64; 83,01</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>65,05; 79,86</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>64,66%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>72,1%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>69,92%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n"/>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>50,5; 76,16</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>63,63; 78,28</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>63,36; 75,95</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="4">
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A4:A5"/>
     <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A14:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -965,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -978,7 +723,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población mayor de 65 años que ha sufrido alguna caída que precise atención sanitaria en el último año</t>
+          <t>Población mayor de 65 años que ha sufrido alguna caída que precise atención sanitaria en el último año (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1027,7 +772,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>16-24</t>
+          <t>65-74</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -1037,17 +782,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>54</t>
         </is>
       </c>
     </row>
@@ -1060,17 +805,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7817</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19752</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>27569</t>
         </is>
       </c>
     </row>
@@ -1083,24 +828,24 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4722; 10581</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>15650; 23190</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>22456; 31951</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>75 o más</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1110,17 +855,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>109</t>
         </is>
       </c>
     </row>
@@ -1133,17 +878,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14238</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>39864</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>54102</t>
         </is>
       </c>
     </row>
@@ -1156,24 +901,24 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10528; 16853</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>35038; 43971</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>47733; 59241</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1183,17 +928,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>123</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>163</t>
         </is>
       </c>
     </row>
@@ -1206,17 +951,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22055</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>59616</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>81671</t>
         </is>
       </c>
     </row>
@@ -1229,403 +974,33 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>17080; 26406</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>53627; 64833</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>74045; 88323</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>45-54</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n"/>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n"/>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>55-64</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n"/>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>65-74</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n"/>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>7817</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>19752</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>27569</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n"/>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>4782; 10740</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>15878; 23119</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>22809; 31663</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>75 o más</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>14238</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>39864</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>54102</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>10722; 17080</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>35287; 43955</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>47935; 58845</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n"/>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>22055</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>59616</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>81671</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n"/>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>17224; 25976</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>52617; 64726</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>74001; 88709</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="4">
+    <mergeCell ref="A1:B2"/>
     <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A4:A6"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A25:A27"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_dic/P15E_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P15E_R-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>63,57%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>35,31; 79,13</t>
+          <t>35,84; 78,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>52,62; 77,97</t>
+          <t>54,39; 78,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52,09; 74,11</t>
+          <t>53,46; 74,54</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>74,23%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>50,77; 81,27</t>
+          <t>51,24; 82,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>66,17; 83,04</t>
+          <t>67,29; 83,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64,78; 80,4</t>
+          <t>66,53; 80,55</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>70,25%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>50,07; 77,42</t>
+          <t>50,16; 75,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>64,85; 78,41</t>
+          <t>65,92; 79,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>63,4; 75,62</t>
+          <t>64,34; 76,08</t>
         </is>
       </c>
     </row>
@@ -805,17 +805,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7817</t>
+          <t>8600</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19752</t>
+          <t>21558</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27569</t>
+          <t>30158</t>
         </is>
       </c>
     </row>
@@ -828,17 +828,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4722; 10581</t>
+          <t>5409; 11889</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15650; 23190</t>
+          <t>17596; 25333</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22456; 31951</t>
+          <t>25363; 35363</t>
         </is>
       </c>
     </row>
@@ -878,17 +878,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>14238</t>
+          <t>15793</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>39864</t>
+          <t>43344</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>54102</t>
+          <t>59137</t>
         </is>
       </c>
     </row>
@@ -901,17 +901,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10528; 16853</t>
+          <t>11791; 18913</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35038; 43971</t>
+          <t>38120; 47164</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>47733; 59241</t>
+          <t>53003; 64174</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22055</t>
+          <t>24393</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>59616</t>
+          <t>64902</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81671</t>
+          <t>89295</t>
         </is>
       </c>
     </row>
@@ -974,17 +974,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17080; 26406</t>
+          <t>19114; 28837</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>53627; 64833</t>
+          <t>58671; 70528</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>74045; 88323</t>
+          <t>81785; 96701</t>
         </is>
       </c>
     </row>
